--- a/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:12:47+00:00</t>
+    <t>2026-03-23T15:20:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:20:38+00:00</t>
+    <t>2026-03-24T09:51:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-1</t>
+    <t>0.7.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T09:51:35+00:00</t>
+    <t>2026-03-24T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:33:49+00:00</t>
+    <t>2026-04-29T13:16:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T13:16:27+00:00</t>
+    <t>2026-04-29T15:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:13+00:00</t>
+    <t>2026-04-29T15:21:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:33+00:00</t>
+    <t>2026-07-23T07:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1019,7 +1019,7 @@
   </si>
   <si>
     <t>CodeableConcept
-QuantityRangeReference(PlanDefinition|ResearchStudy|InsurancePlan|HealthcareService|Group|Location|Organization)</t>
+QuantityRangeReference(PlanDefinition|4.0.1|ResearchStudy|4.0.1|InsurancePlan|4.0.1|HealthcareService|4.0.1|Group|4.0.1|Location|4.0.1|Organization|4.0.1)</t>
   </si>
   <si>
     <t>Value that defines the context</t>
@@ -1034,7 +1034,7 @@
     <t>A code that defines the specific value for the context being specified.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/use-context</t>
+    <t>http://hl7.org/fhir/ValueSet/use-context|4.0.1</t>
   </si>
   <si>
     <t>UsageContext.value[x]</t>
@@ -2481,15 +2481,15 @@
   <dimension ref="A1:AO142"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="84.98828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="56.85546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="72.859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.7421875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2500,27 +2500,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="86.3125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="96.27734375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="207.046875" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.5390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="73.99609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="82.5390625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="177.5078125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.04296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="125.9375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="48.05859375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="56.63671875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="107.96875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="48.5546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3814,7 +3814,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>152</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>157</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>168</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>172</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>177</v>
       </c>
@@ -4639,7 +4639,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>190</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>198</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>207</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>215</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>221</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>234</v>
       </c>
@@ -5581,7 +5581,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>250</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>259</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>268</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>283</v>
       </c>
@@ -10348,7 +10348,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>392</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>405</v>
       </c>
@@ -10699,7 +10699,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>412</v>
       </c>
@@ -10818,7 +10818,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>419</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>433</v>
       </c>
@@ -11637,7 +11637,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
         <v>446</v>
       </c>
@@ -11756,7 +11756,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>453</v>
       </c>
@@ -15498,7 +15498,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
         <v>548</v>
       </c>
@@ -15617,7 +15617,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>554</v>
       </c>
@@ -15855,7 +15855,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>565</v>
       </c>
@@ -15974,7 +15974,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
         <v>572</v>
       </c>
@@ -16091,7 +16091,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
         <v>576</v>
       </c>
@@ -16210,7 +16210,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>584</v>
       </c>
@@ -17027,7 +17027,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
         <v>609</v>
       </c>
@@ -17144,7 +17144,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
         <v>615</v>
       </c>
@@ -17263,7 +17263,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
         <v>621</v>
       </c>
@@ -17384,7 +17384,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
         <v>627</v>
       </c>
@@ -17503,7 +17503,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
         <v>633</v>
       </c>
@@ -17620,7 +17620,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
         <v>639</v>
       </c>
@@ -17737,7 +17737,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="131" hidden="true">
+    <row r="131">
       <c r="A131" t="s" s="2">
         <v>645</v>
       </c>
@@ -18322,7 +18322,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
         <v>657</v>
       </c>
@@ -18441,7 +18441,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
         <v>662</v>
       </c>
@@ -18911,7 +18911,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
         <v>671</v>
       </c>
@@ -19028,7 +19028,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="142" hidden="true">
+    <row r="142">
       <c r="A142" t="s" s="2">
         <v>676</v>
       </c>
@@ -19149,12 +19149,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO142">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:54:45+00:00</t>
+    <t>2026-07-23T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-questionnaire-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:00:07+00:00</t>
+    <t>2026-07-23T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
